--- a/docs/03_test/従業員削除のテストケース.xlsx
+++ b/docs/03_test/従業員削除のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1273EAB3-88B7-4A2F-AAF9-206A1EC37D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3988998-4A5D-4779-BD4E-75519B7F3856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>手順No.</t>
     <rPh sb="0" eb="2">
@@ -249,37 +249,65 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「○○（ここだけ確認して後ほど入力）」をプルダウンで選択して完了ボタンを押す</t>
-    <rPh sb="8" eb="10">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ノチ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="26" eb="28">
+    <t>「1:田中太郎 / 経理部」をプルダウンで選択して完了ボタンを押す</t>
+    <rPh sb="3" eb="7">
+      <t>タナカタロウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ケイリブ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
       <t>センタク</t>
     </rPh>
-    <rPh sb="30" eb="32">
+    <rPh sb="25" eb="27">
       <t>カンリョウ</t>
     </rPh>
-    <rPh sb="36" eb="37">
+    <rPh sb="31" eb="32">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「○○（ここだけ確認して後ほど入力）」をプルダウンで選択して完了ボタンを押す</t>
-    <rPh sb="26" eb="28">
+    <t>「2:鈴木三郎 / 総務部」をプルダウンで選択して完了ボタンを押す</t>
+    <rPh sb="3" eb="5">
+      <t>スズキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サブロウ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>ソウムブ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
       <t>センタク</t>
     </rPh>
-    <rPh sb="30" eb="32">
+    <rPh sb="25" eb="27">
       <t>カンリョウ</t>
     </rPh>
-    <rPh sb="36" eb="37">
+    <rPh sb="31" eb="32">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次：テストケース一覧（クリックで該当のテストケースに遷移します）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①正常系その1：削除完了後に続けて削除するパターン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>②正常系その2：削除完了後にメニューに戻るパターン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目次に戻る</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>モド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -288,7 +316,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +329,14 @@
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -327,17 +363,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -347,8 +378,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -362,6 +407,451 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1784351</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>728573</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB29DD62-DDD3-4B0E-B76E-34ACCCFB6B97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5289551" y="685800"/>
+          <a:ext cx="1784350" cy="728573"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>41085</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>774700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{445BED28-2FA9-13D7-C104-955402C5F775}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5289551" y="1746251"/>
+          <a:ext cx="1869884" cy="774699"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1746250</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>663187</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F576111E-F6D2-DEFC-AFED-9E79184AB4DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5289551" y="2806700"/>
+          <a:ext cx="1746249" cy="663187"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1759655</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>736601</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCD3F8E6-6DB8-2D7A-3A26-0CC31A40D8ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5289550" y="3867151"/>
+          <a:ext cx="1759655" cy="736600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1752600</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>937832</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63DC5BFF-7D2B-A6C7-C84E-2CF033770329}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5289550" y="4927600"/>
+          <a:ext cx="1752600" cy="937832"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1748367</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>666750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24BBD148-13E6-5DF1-07D7-B19FE4DE3BEC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5289550" y="5988050"/>
+          <a:ext cx="1748367" cy="666750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>18143</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>716219</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4A9F17F-CD1F-BE9C-C140-D2FC8512B308}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5288643" y="7311571"/>
+          <a:ext cx="1850571" cy="716219"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>729391</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1608211D-E213-CC2E-11CB-8E3A11A699EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5288643" y="8372929"/>
+          <a:ext cx="1832428" cy="729391"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1788100</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>952499</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE3ECB65-190D-8C27-9E56-C41AEF878700}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5288643" y="9434286"/>
+          <a:ext cx="1788100" cy="952499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1823357</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>438826</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D91E83-80C9-D44E-2631-58C529572F96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5288643" y="10495643"/>
+          <a:ext cx="1823357" cy="438826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -627,167 +1117,214 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" style="5" customWidth="1"/>
-    <col min="4" max="5" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="28.83203125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
+    <row r="8" spans="1:5" ht="83.5" customHeight="1">
+      <c r="A8">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="54">
-      <c r="A5">
+    <row r="9" spans="1:5" ht="83.5" customHeight="1">
+      <c r="A9">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="36">
-      <c r="A6">
+    <row r="10" spans="1:5" ht="83.5" customHeight="1">
+      <c r="A10">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
+    <row r="11" spans="1:5" ht="83.5" customHeight="1">
+      <c r="A11">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
+    <row r="12" spans="1:5" ht="83.5" customHeight="1">
+      <c r="A12">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
+    <row r="13" spans="1:5" ht="83.5" customHeight="1">
+      <c r="A13">
         <v>6</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="20.5" customHeight="1">
+      <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="83.5" customHeight="1">
+      <c r="A15">
         <v>1</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="54">
-      <c r="A12">
+    <row r="16" spans="1:5" ht="83.5" customHeight="1">
+      <c r="A16">
         <v>2</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="36">
-      <c r="A13">
+    <row r="17" spans="1:3" ht="83.5" customHeight="1">
+      <c r="A17">
         <v>3</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14">
+    <row r="18" spans="1:3" ht="83.5" customHeight="1">
+      <c r="A18">
         <v>4</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="A3" location="Sheet1!A6" display="①正常系その1：削除完了後に続けて削除するパターン" xr:uid="{2A55B932-AC2F-493B-834B-F00159C81543}"/>
+    <hyperlink ref="A4" location="Sheet1!A14" display="②正常系その2：削除完了後にメニューに戻るパターン" xr:uid="{AAF53404-6805-4868-9CE4-84E3EDD462F0}"/>
+    <hyperlink ref="E6" location="Sheet1!A2" display="目次に戻る" xr:uid="{8EC0F8EA-1AD3-465B-830C-ABA601BD2FB2}"/>
+    <hyperlink ref="E14" location="Sheet1!A2" display="目次に戻る" xr:uid="{A881EA69-7682-42EB-B4E3-065AD05CC283}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/03_test/従業員削除のテストケース.xlsx
+++ b/docs/03_test/従業員削除のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3988998-4A5D-4779-BD4E-75519B7F3856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E175BF3E-CD5B-45B2-9A75-5C3E9388A88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>手順No.</t>
     <rPh sb="0" eb="2">
@@ -68,25 +68,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面上部の従業員削除ボタンを押す</t>
-    <rPh sb="0" eb="2">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジョウブ</t>
-    </rPh>
-    <rPh sb="5" eb="8">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>確認画面に遷移する</t>
     <rPh sb="0" eb="2">
       <t>カクニン</t>
@@ -100,22 +81,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員削除画面に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>戻るボタンを押す</t>
     <rPh sb="0" eb="1">
       <t>モド</t>
@@ -126,35 +91,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>入力値を保持したまま従業員削除画面に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>ニュウリョクチ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ホジ</t>
-    </rPh>
-    <rPh sb="10" eb="15">
-      <t>ジュウギョウインサクジョ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>そのまま完了ボタンを押す</t>
-    <rPh sb="4" eb="6">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>削除ボタンを押す</t>
     <rPh sb="0" eb="2">
       <t>サクジョ</t>
@@ -178,19 +114,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>続けて削除するボタンを押す</t>
-    <rPh sb="0" eb="1">
-      <t>ツヅ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>①正常系その1：削除完了後に続けて削除するパターン</t>
     <rPh sb="0" eb="4">
       <t>マルイチセイジョウケイ</t>
@@ -210,95 +133,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>②正常系その2：削除完了後にメニューに戻るパターン</t>
-    <rPh sb="1" eb="3">
-      <t>セイジョウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ケイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>カンリョウゴ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メニューに戻るボタンを押す</t>
-    <rPh sb="5" eb="6">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メニュー画面に戻る</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「1:田中太郎 / 経理部」をプルダウンで選択して完了ボタンを押す</t>
-    <rPh sb="3" eb="7">
-      <t>タナカタロウ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>ケイリブ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>「2:鈴木三郎 / 総務部」をプルダウンで選択して完了ボタンを押す</t>
-    <rPh sb="3" eb="5">
-      <t>スズキ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>サブロウ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>ソウムブ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="31" eb="32">
-      <t>オ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>目次：テストケース一覧（クリックで該当のテストケースに遷移します）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>①正常系その1：削除完了後に続けて削除するパターン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>②正常系その2：削除完了後にメニューに戻るパターン</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -308,6 +143,93 @@
     </rPh>
     <rPh sb="3" eb="4">
       <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①正常</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の従業員一覧ボタンを押す</t>
+    <rPh sb="0" eb="2">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウブ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員一覧に遷移する</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員ID：1の社員の削除ボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>もう一度従業員ID：1の社員の削除ボタンを押す</t>
+    <rPh sb="2" eb="4">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>従業員一覧に戻るボタンを押す</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウギョウイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -378,12 +300,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -391,6 +307,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -414,22 +336,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>27214</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1784351</xdr:colOff>
+      <xdr:colOff>1505857</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>728573</xdr:rowOff>
+      <xdr:rowOff>893229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB29DD62-DDD3-4B0E-B76E-34ACCCFB6B97}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7FB086E-4FA7-D000-3BD7-A264277FA77F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -445,8 +367,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289551" y="685800"/>
-          <a:ext cx="1784350" cy="728573"/>
+          <a:off x="5315857" y="1587500"/>
+          <a:ext cx="1478643" cy="893229"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -463,17 +385,17 @@
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>41085</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1729810</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>774700</xdr:rowOff>
+      <xdr:rowOff>734787</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
+        <xdr:cNvPr id="13" name="図 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{445BED28-2FA9-13D7-C104-955402C5F775}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5917069D-94AB-0395-ACA7-7E113D96B89C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -489,8 +411,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289551" y="1746251"/>
-          <a:ext cx="1869884" cy="774699"/>
+          <a:off x="5288644" y="2648858"/>
+          <a:ext cx="1729809" cy="734786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -502,22 +424,110 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1746250</xdr:colOff>
+      <xdr:colOff>1478643</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>663187</xdr:rowOff>
+      <xdr:rowOff>893229</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
+        <xdr:cNvPr id="14" name="図 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F576111E-F6D2-DEFC-AFED-9E79184AB4DE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E116D055-A29B-4750-860C-814C058A7E6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5288643" y="3710214"/>
+          <a:ext cx="1478643" cy="893229"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1729809</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>734786</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17EAB2DA-5B10-4E42-B15A-BF37952ED0C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5288643" y="4771571"/>
+          <a:ext cx="1729809" cy="734786"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1605643</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>877082</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{773164CA-646C-C71E-818C-51BD49E046D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -533,8 +543,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289551" y="2806700"/>
-          <a:ext cx="1746249" cy="663187"/>
+          <a:off x="5288643" y="5832929"/>
+          <a:ext cx="1605643" cy="877082"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -547,21 +557,21 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1759655</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>736601</xdr:rowOff>
+      <xdr:colOff>1596571</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>911753</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="17" name="図 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCD3F8E6-6DB8-2D7A-3A26-0CC31A40D8ED}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{931A1CE5-5D49-A07C-E636-57E6C9629B84}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -577,272 +587,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5289550" y="3867151"/>
-          <a:ext cx="1759655" cy="736600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1752600</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>937832</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63DC5BFF-7D2B-A6C7-C84E-2CF033770329}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5289550" y="4927600"/>
-          <a:ext cx="1752600" cy="937832"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1748367</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>666750</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24BBD148-13E6-5DF1-07D7-B19FE4DE3BEC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5289550" y="5988050"/>
-          <a:ext cx="1748367" cy="666750"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>18143</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>716219</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4A9F17F-CD1F-BE9C-C140-D2FC8512B308}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5288643" y="7311571"/>
-          <a:ext cx="1850571" cy="716219"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>729391</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1608211D-E213-CC2E-11CB-8E3A11A699EC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5288643" y="8372929"/>
-          <a:ext cx="1832428" cy="729391"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1788100</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>952499</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE3ECB65-190D-8C27-9E56-C41AEF878700}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5288643" y="9434286"/>
-          <a:ext cx="1788100" cy="952499"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1823357</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>438826</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92D91E83-80C9-D44E-2631-58C529572F96}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5288643" y="10495643"/>
-          <a:ext cx="1823357" cy="438826"/>
+          <a:off x="5288643" y="6894286"/>
+          <a:ext cx="1596571" cy="911753"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1117,44 +863,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="28.83203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="4" max="4" width="22.9140625" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6" t="s">
-        <v>20</v>
+      <c r="A2" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="7" t="s">
-        <v>21</v>
+      <c r="A3" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="A4" s="5"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1166,14 +910,14 @@
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="8" t="s">
-        <v>23</v>
+      <c r="A6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1195,10 +939,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="83.5" customHeight="1">
@@ -1206,10 +950,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="83.5" customHeight="1">
@@ -1217,10 +961,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="83.5" customHeight="1">
@@ -1228,10 +972,10 @@
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="83.5" customHeight="1">
@@ -1239,10 +983,10 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="83.5" customHeight="1">
@@ -1250,79 +994,21 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="20.5" customHeight="1">
-      <c r="A14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="83.5" customHeight="1">
-      <c r="A15">
-        <v>1</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="83.5" customHeight="1">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="83.5" customHeight="1">
-      <c r="A17">
-        <v>3</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="83.5" customHeight="1">
-      <c r="A18">
-        <v>4</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="A3" location="Sheet1!A6" display="①正常系その1：削除完了後に続けて削除するパターン" xr:uid="{2A55B932-AC2F-493B-834B-F00159C81543}"/>
-    <hyperlink ref="A4" location="Sheet1!A14" display="②正常系その2：削除完了後にメニューに戻るパターン" xr:uid="{AAF53404-6805-4868-9CE4-84E3EDD462F0}"/>
     <hyperlink ref="E6" location="Sheet1!A2" display="目次に戻る" xr:uid="{8EC0F8EA-1AD3-465B-830C-ABA601BD2FB2}"/>
-    <hyperlink ref="E14" location="Sheet1!A2" display="目次に戻る" xr:uid="{A881EA69-7682-42EB-B4E3-065AD05CC283}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/docs/03_test/従業員削除のテストケース.xlsx
+++ b/docs/03_test/従業員削除のテストケース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E175BF3E-CD5B-45B2-9A75-5C3E9388A88D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09143CF5-D9CE-49D7-A7D3-883ABF92546A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,16 +34,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員削除テストケース</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>手順</t>
     <rPh sb="0" eb="2">
       <t>テジュン</t>
@@ -151,84 +141,76 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>画面上部の従業員一覧ボタンを押す</t>
+    <t>社員削除テストケース</t>
+    <rPh sb="2" eb="4">
+      <t>サクジョ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>画面上部の社員一覧ボタンを押す</t>
     <rPh sb="0" eb="2">
       <t>ガメン</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>ジョウブ</t>
     </rPh>
-    <rPh sb="5" eb="8">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
+    <rPh sb="7" eb="9">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="14" eb="15">
+    <rPh sb="13" eb="14">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員一覧に遷移する</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
+    <t>社員一覧に遷移する</t>
+    <rPh sb="2" eb="4">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="6" eb="8">
+    <rPh sb="5" eb="7">
       <t>センイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員ID：1の社員の削除ボタンを押す</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
+    <t>社員ID：1の社員の削除ボタンを押す</t>
+    <rPh sb="7" eb="9">
       <t>シャイン</t>
     </rPh>
-    <rPh sb="11" eb="13">
+    <rPh sb="10" eb="12">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="17" eb="18">
+    <rPh sb="16" eb="17">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>もう一度従業員ID：1の社員の削除ボタンを押す</t>
+    <t>もう一度社員ID：1の社員の削除ボタンを押す</t>
     <rPh sb="2" eb="4">
       <t>イチド</t>
     </rPh>
-    <rPh sb="4" eb="7">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
+    <rPh sb="11" eb="13">
       <t>シャイン</t>
     </rPh>
-    <rPh sb="15" eb="17">
+    <rPh sb="14" eb="16">
       <t>サクジョ</t>
     </rPh>
-    <rPh sb="21" eb="22">
+    <rPh sb="20" eb="21">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>従業員一覧に戻るボタンを押す</t>
-    <rPh sb="0" eb="3">
-      <t>ジュウギョウイン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
+    <t>社員一覧に戻るボタンを押す</t>
+    <rPh sb="2" eb="4">
       <t>イチラン</t>
     </rPh>
-    <rPh sb="6" eb="7">
+    <rPh sb="5" eb="6">
       <t>モド</t>
     </rPh>
-    <rPh sb="12" eb="13">
+    <rPh sb="11" eb="12">
       <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -336,22 +318,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>27214</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1505857</xdr:colOff>
+      <xdr:colOff>2182091</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>893229</xdr:rowOff>
+      <xdr:rowOff>760383</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7FB086E-4FA7-D000-3BD7-A264277FA77F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3115B11B-3EED-E05D-608D-3F0BF22D3DF4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -367,8 +349,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5315857" y="1587500"/>
-          <a:ext cx="1478643" cy="893229"/>
+          <a:off x="5287818" y="1616364"/>
+          <a:ext cx="2182091" cy="760383"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -380,22 +362,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1729810</xdr:colOff>
+      <xdr:colOff>2205182</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>734787</xdr:rowOff>
+      <xdr:rowOff>561467</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="図 12">
+        <xdr:cNvPr id="4" name="図 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5917069D-94AB-0395-ACA7-7E113D96B89C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46C08EC4-9EF9-1A1C-B7D9-8D139626B6D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -411,8 +393,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5288644" y="2648858"/>
-          <a:ext cx="1729809" cy="734786"/>
+          <a:off x="5287818" y="2678545"/>
+          <a:ext cx="2205182" cy="561467"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -430,104 +412,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1478643</xdr:colOff>
+      <xdr:colOff>2193637</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>893229</xdr:rowOff>
+      <xdr:rowOff>773074</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="図 13">
+        <xdr:cNvPr id="5" name="図 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E116D055-A29B-4750-860C-814C058A7E6B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5288643" y="3710214"/>
-          <a:ext cx="1478643" cy="893229"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1729809</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>734786</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="図 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17EAB2DA-5B10-4E42-B15A-BF37952ED0C8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5288643" y="4771571"/>
-          <a:ext cx="1729809" cy="734786"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1605643</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>877082</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="図 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{773164CA-646C-C71E-818C-51BD49E046D9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7C8972B-AA93-49A4-7DD4-62219991CE51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -543,8 +437,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5288643" y="5832929"/>
-          <a:ext cx="1605643" cy="877082"/>
+          <a:off x="5287818" y="3740727"/>
+          <a:ext cx="2193637" cy="773074"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -556,22 +450,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>1596571</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>911753</xdr:rowOff>
+      <xdr:colOff>2205183</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>563620</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="図 16">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{931A1CE5-5D49-A07C-E636-57E6C9629B84}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A384D501-15C5-ABFB-4FC1-0148D7C4D311}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -587,8 +481,96 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5288643" y="6894286"/>
-          <a:ext cx="1596571" cy="911753"/>
+          <a:off x="5287819" y="4802910"/>
+          <a:ext cx="2205182" cy="563619"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2239818</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>726652</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2532E05B-BAC6-8C25-C374-1183D24405BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5287818" y="5865091"/>
+          <a:ext cx="2239818" cy="726652"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2228630</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>692727</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C436683B-F67E-418D-0E82-88739C5DBB6E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5287818" y="6927273"/>
+          <a:ext cx="2228630" cy="692727"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -869,13 +851,13 @@
     <col min="1" max="1" width="7.75" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="28.83203125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.9140625" customWidth="1"/>
+    <col min="4" max="4" width="29.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="8" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -883,7 +865,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -891,7 +873,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -911,13 +893,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -925,13 +907,13 @@
         <v>0</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="83.5" customHeight="1">
@@ -953,7 +935,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="83.5" customHeight="1">
@@ -961,7 +943,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>14</v>
@@ -975,7 +957,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="83.5" customHeight="1">
@@ -983,10 +965,10 @@
         <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="83.5" customHeight="1">
